--- a/customer_satisfaction_evaluation_forms/007_utility_service_satisfaction_survey--customer_satisfaction_evaluation_forms.xlsx
+++ b/customer_satisfaction_evaluation_forms/007_utility_service_satisfaction_survey--customer_satisfaction_evaluation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1106,8 +1106,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Very satisfied'}</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Somewhat satisfied'}</t>
+          <t>Somewhat satisfied</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_dissatisfied'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Somewhat dissatisfied'}</t>
+          <t>Somewhat dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Very dissatisfied'}</t>
+          <t>Very dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1254,12 +1254,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'very_reliable'}</t>
+          <t>very_reliable</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Very reliable'}</t>
+          <t>Very reliable</t>
         </is>
       </c>
     </row>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_reliable'}</t>
+          <t>somewhat_reliable</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Somewhat reliable'}</t>
+          <t>Somewhat reliable</t>
         </is>
       </c>
     </row>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1339,12 +1339,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_unreliable'}</t>
+          <t>somewhat_unreliable</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Somewhat unreliable'}</t>
+          <t>Somewhat unreliable</t>
         </is>
       </c>
     </row>
@@ -1356,12 +1356,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'very_unreliable'}</t>
+          <t>very_unreliable</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Very unreliable'}</t>
+          <t>Very unreliable</t>
         </is>
       </c>
     </row>
@@ -1373,12 +1373,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1407,12 +1407,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'chat'}</t>
+          <t>chat</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Chat'}</t>
+          <t>Chat</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'in-person'}</t>
+          <t>in-person</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'In-person'}</t>
+          <t>In-person</t>
         </is>
       </c>
     </row>
@@ -1441,12 +1441,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1458,12 +1458,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1475,12 +1475,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1492,12 +1492,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1509,12 +1509,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'Very satisfied'}</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'Somewhat satisfied'}</t>
+          <t>Somewhat satisfied</t>
         </is>
       </c>
     </row>
@@ -1543,12 +1543,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1560,12 +1560,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_dissatisfied'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 'Somewhat dissatisfied'}</t>
+          <t>Somewhat dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1577,12 +1577,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 'Very dissatisfied'}</t>
+          <t>Very dissatisfied</t>
         </is>
       </c>
     </row>
